--- a/Plannings 2026 S20.xlsx
+++ b/Plannings 2026 S20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D76AC588-95F3-4345-92E4-96684B0CB1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{D76AC588-95F3-4345-92E4-96684B0CB1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2A9CE38-A8D2-4D4D-8634-2C2CEF98AAD1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="106">
   <si>
     <t>Planning des salariés du 11/05/2026 au 17/05/2026</t>
   </si>
@@ -349,7 +349,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -438,6 +438,12 @@
     <font>
       <sz val="8"/>
       <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -772,7 +778,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -953,6 +959,9 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4622,6 +4631,50 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2342029" y="5636559"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F0A3FFB-1423-45E2-B0B1-8A80A2C86894}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7026088" y="3316941"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5282,7 +5335,9 @@
       <c r="A18" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="21"/>
+      <c r="B18" s="21" t="s">
+        <v>13</v>
+      </c>
       <c r="C18" s="21"/>
       <c r="D18" s="21" t="s">
         <v>13</v>
@@ -5296,7 +5351,9 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="27"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="62" t="s">
+        <v>68</v>
+      </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
         <v>35</v>
@@ -6786,13 +6843,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E0D53BC-C34C-4902-9CAE-E951C8911F64}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B0DD343-E130-45B5-84B4-EBCC15E4C2EF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA22322-5C77-4CB0-93E0-631958536DF1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE0FF401-2928-43D9-8A98-35A81B038ECB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ED5375D-3A3C-4A2A-96C0-A18320FFF873}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6003F7E4-418D-4F95-AF6D-767ABA8B20CF}"/>
 </file>
--- a/Plannings 2026 S20.xlsx
+++ b/Plannings 2026 S20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{D76AC588-95F3-4345-92E4-96684B0CB1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2A9CE38-A8D2-4D4D-8634-2C2CEF98AAD1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D76AC588-95F3-4345-92E4-96684B0CB1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="106">
   <si>
     <t>Planning des salariés du 11/05/2026 au 17/05/2026</t>
   </si>
@@ -349,7 +349,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -438,12 +438,6 @@
     <font>
       <sz val="8"/>
       <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -778,7 +772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -959,9 +953,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4631,50 +4622,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2342029" y="5636559"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F0A3FFB-1423-45E2-B0B1-8A80A2C86894}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7026088" y="3316941"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5335,9 +5282,7 @@
       <c r="A18" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>13</v>
-      </c>
+      <c r="B18" s="21"/>
       <c r="C18" s="21"/>
       <c r="D18" s="21" t="s">
         <v>13</v>
@@ -5351,9 +5296,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="27"/>
-      <c r="B19" s="62" t="s">
-        <v>68</v>
-      </c>
+      <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
         <v>35</v>
@@ -6843,13 +6786,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B0DD343-E130-45B5-84B4-EBCC15E4C2EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E0D53BC-C34C-4902-9CAE-E951C8911F64}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE0FF401-2928-43D9-8A98-35A81B038ECB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA22322-5C77-4CB0-93E0-631958536DF1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6003F7E4-418D-4F95-AF6D-767ABA8B20CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ED5375D-3A3C-4A2A-96C0-A18320FFF873}"/>
 </file>
--- a/Plannings 2026 S20.xlsx
+++ b/Plannings 2026 S20.xlsx
@@ -6843,13 +6843,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B0DD343-E130-45B5-84B4-EBCC15E4C2EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3A6DD73-BBA7-4331-B15C-0991A285E317}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE0FF401-2928-43D9-8A98-35A81B038ECB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9FE7FFE-813D-4603-8F6D-78FF7433446C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6003F7E4-418D-4F95-AF6D-767ABA8B20CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FA30EAA-0464-4935-BF60-D7EB65711FFF}"/>
 </file>
--- a/Plannings 2026 S20.xlsx
+++ b/Plannings 2026 S20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{D76AC588-95F3-4345-92E4-96684B0CB1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2A9CE38-A8D2-4D4D-8634-2C2CEF98AAD1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D76AC588-95F3-4345-92E4-96684B0CB1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="106">
   <si>
     <t>Planning des salariés du 11/05/2026 au 17/05/2026</t>
   </si>
@@ -349,7 +349,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -438,12 +438,6 @@
     <font>
       <sz val="8"/>
       <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -778,7 +772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -959,9 +953,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4631,50 +4622,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2342029" y="5636559"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F0A3FFB-1423-45E2-B0B1-8A80A2C86894}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7026088" y="3316941"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5335,9 +5282,7 @@
       <c r="A18" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>13</v>
-      </c>
+      <c r="B18" s="21"/>
       <c r="C18" s="21"/>
       <c r="D18" s="21" t="s">
         <v>13</v>
@@ -5351,9 +5296,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="27"/>
-      <c r="B19" s="62" t="s">
-        <v>68</v>
-      </c>
+      <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
         <v>35</v>
@@ -6843,13 +6786,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3A6DD73-BBA7-4331-B15C-0991A285E317}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E0D53BC-C34C-4902-9CAE-E951C8911F64}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9FE7FFE-813D-4603-8F6D-78FF7433446C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA22322-5C77-4CB0-93E0-631958536DF1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FA30EAA-0464-4935-BF60-D7EB65711FFF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5ED5375D-3A3C-4A2A-96C0-A18320FFF873}"/>
 </file>
--- a/Plannings 2026 S20.xlsx
+++ b/Plannings 2026 S20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{D76AC588-95F3-4345-92E4-96684B0CB1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2A9CE38-A8D2-4D4D-8634-2C2CEF98AAD1}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{D76AC588-95F3-4345-92E4-96684B0CB1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{510CB741-342C-45F1-A3F5-A47BEEA5EB55}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="105">
   <si>
     <t>Planning des salariés du 11/05/2026 au 17/05/2026</t>
   </si>
@@ -220,9 +220,6 @@
   </si>
   <si>
     <t>ORDONEZ GOMEZ Oceane</t>
-  </si>
-  <si>
-    <t>19:30/21:30</t>
   </si>
   <si>
     <t>PEREZ Loic</t>
@@ -5086,22 +5083,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>102</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>103</v>
       </c>
       <c r="H3" s="15" t="s">
         <v>34</v>
@@ -5352,7 +5349,7 @@
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="27"/>
       <c r="B19" s="62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
@@ -5770,7 +5767,7 @@
       <c r="B48" s="25"/>
       <c r="C48" s="25"/>
       <c r="D48" s="46" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="E48" s="25"/>
       <c r="F48" s="25"/>
@@ -5779,7 +5776,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B49" s="21" t="s">
         <v>13</v>
@@ -5804,7 +5801,7 @@
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="24"/>
       <c r="B50" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C50" s="57" t="s">
         <v>22</v>
@@ -5813,19 +5810,19 @@
         <v>19</v>
       </c>
       <c r="E50" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F50" s="25"/>
       <c r="G50" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="H50" s="26" t="s">
         <v>70</v>
-      </c>
-      <c r="H50" s="26" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B51" s="36"/>
       <c r="C51" s="37"/>
@@ -5837,7 +5834,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B52" s="21"/>
       <c r="C52" s="21" t="s">
@@ -5847,7 +5844,7 @@
         <v>13</v>
       </c>
       <c r="E52" s="60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F52" s="21"/>
       <c r="G52" s="21" t="s">
@@ -5859,17 +5856,17 @@
       <c r="A53" s="27"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E53" s="61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H53" s="28"/>
     </row>
@@ -5891,7 +5888,7 @@
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
       <c r="E55" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F55" s="25"/>
       <c r="G55" s="25"/>
@@ -5899,7 +5896,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B56" s="47" t="s">
         <v>50</v>
@@ -5933,7 +5930,7 @@
     </row>
     <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B58" s="31"/>
       <c r="C58" s="32"/>
@@ -5945,7 +5942,7 @@
     </row>
     <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B59" s="31"/>
       <c r="C59" s="32"/>
@@ -5957,7 +5954,7 @@
     </row>
     <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B60" s="31"/>
       <c r="C60" s="32"/>
@@ -5969,7 +5966,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="47" t="s">
@@ -5987,12 +5984,12 @@
       <c r="A62" s="27"/>
       <c r="B62" s="1"/>
       <c r="C62" s="45" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="28"/>
@@ -6013,7 +6010,7 @@
       <c r="A64" s="24"/>
       <c r="B64" s="25"/>
       <c r="C64" s="25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D64" s="25"/>
       <c r="E64" s="25"/>
@@ -6023,7 +6020,7 @@
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B65" s="31"/>
       <c r="C65" s="32"/>
@@ -6093,7 +6090,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -6101,7 +6098,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -6112,16 +6109,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6449,7 +6446,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -6466,7 +6463,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -6483,7 +6480,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -6500,7 +6497,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -6517,7 +6514,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -6534,7 +6531,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -6551,7 +6548,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -6568,7 +6565,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -6585,7 +6582,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -6635,40 +6632,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>94</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>100</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -6843,13 +6840,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3A6DD73-BBA7-4331-B15C-0991A285E317}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8706173A-32BA-4DE5-A364-2896B066D0DF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9FE7FFE-813D-4603-8F6D-78FF7433446C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F94FECF2-B65D-42AB-8CF2-251928A74D10}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FA30EAA-0464-4935-BF60-D7EB65711FFF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23AC4F8A-8CB4-40C2-9E54-66A5F6C66A88}"/>
 </file>
--- a/Plannings 2026 S20.xlsx
+++ b/Plannings 2026 S20.xlsx
@@ -6840,13 +6840,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8706173A-32BA-4DE5-A364-2896B066D0DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67F24E5D-7870-4CBF-BFC1-437D1BEA5DE5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F94FECF2-B65D-42AB-8CF2-251928A74D10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8912316-3C4E-4120-B8E9-DCCD4B41853B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23AC4F8A-8CB4-40C2-9E54-66A5F6C66A88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34BCCC27-C470-420D-944E-028367721AAE}"/>
 </file>